--- a/scripts/fixtures/recebimentos-exemplo.xlsx
+++ b/scripts/fixtures/recebimentos-exemplo.xlsx
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Conta - Banco Exemplo PJ</t>
+          <t>Conta - Inter PF (LUS)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1703,13 +1703,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EEADB61-B370-49BC-9704-7FD641ABCA0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA96E5B2-58B8-4A36-9464-26554BC8F0A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE14050-3424-4474-AD79-554908DEC197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9230C925-05AB-4AAD-BF80-098218274481}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2EE7FF-9026-4D47-A684-1F10F503276C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49A8C8AD-CCD4-4094-BA5D-4446BA197B37}"/>
 </file>